--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1303-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1303-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF9EBD2B-194E-4C4A-B029-5A5F2F9D2E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D40B3AE-2E29-477C-9DB7-6252F041DCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{544223F8-8BEB-44B1-9946-FA5D7B174D3F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{BA6E8B8B-A128-4AA5-987D-074DB5AC2587}"/>
   </bookViews>
   <sheets>
     <sheet name="1303-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1616,27 +1616,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B8E1724-243D-4272-957A-7DEC03A74E00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02268557-4768-4DDB-BEF2-128BE82F3704}">
   <dimension ref="A1:X56"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1670,7 +1669,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1706,7 +1705,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1758,7 +1757,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1826,7 +1825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1898,7 +1897,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1970,7 +1969,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2114,7 +2113,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2330,7 +2329,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2618,7 +2617,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3266,7 +3265,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2002</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3510,7 +3509,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2001</v>
       </c>
@@ -3582,7 +3581,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -3654,7 +3653,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1999</v>
       </c>
@@ -3726,7 +3725,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1997</v>
       </c>
@@ -3870,7 +3869,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>1996</v>
       </c>
@@ -3942,7 +3941,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="43"/>
       <c r="B35" s="44"/>
       <c r="C35" s="18" t="s">
@@ -3970,7 +3969,7 @@
       <c r="W35" s="50"/>
       <c r="X35" s="46"/>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>1995</v>
       </c>
@@ -4042,7 +4041,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="55"/>
       <c r="B37" s="56"/>
       <c r="C37" s="20" t="s">
@@ -4070,7 +4069,7 @@
       <c r="W37" s="62"/>
       <c r="X37" s="58"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1994</v>
       </c>
@@ -4142,7 +4141,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="43"/>
       <c r="B39" s="44"/>
       <c r="C39" s="18" t="s">
@@ -4170,7 +4169,7 @@
       <c r="W39" s="50"/>
       <c r="X39" s="46"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>1993</v>
       </c>
@@ -4242,7 +4241,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="55"/>
       <c r="B41" s="56"/>
       <c r="C41" s="20" t="s">
@@ -4270,7 +4269,7 @@
       <c r="W41" s="62"/>
       <c r="X41" s="58"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>1992</v>
       </c>
@@ -4342,7 +4341,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="43"/>
       <c r="B43" s="44"/>
       <c r="C43" s="18" t="s">
@@ -4370,7 +4369,7 @@
       <c r="W43" s="50"/>
       <c r="X43" s="46"/>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>1991</v>
       </c>
@@ -4442,7 +4441,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="55"/>
       <c r="B45" s="56"/>
       <c r="C45" s="20" t="s">
@@ -4470,7 +4469,7 @@
       <c r="W45" s="62"/>
       <c r="X45" s="58"/>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>1990</v>
       </c>
@@ -4542,7 +4541,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="43"/>
       <c r="B47" s="44"/>
       <c r="C47" s="18" t="s">
@@ -4570,7 +4569,7 @@
       <c r="W47" s="50"/>
       <c r="X47" s="46"/>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>1989</v>
       </c>
@@ -4642,7 +4641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="55"/>
       <c r="B49" s="56"/>
       <c r="C49" s="20" t="s">
@@ -4670,7 +4669,7 @@
       <c r="W49" s="62"/>
       <c r="X49" s="58"/>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1988</v>
       </c>
@@ -4742,7 +4741,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>1987</v>
       </c>
@@ -4814,7 +4813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>1986</v>
       </c>
@@ -4886,7 +4885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>1985</v>
       </c>
@@ -4958,7 +4957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>1984</v>
       </c>
@@ -5030,7 +5029,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="39">
         <v>1983</v>
       </c>
@@ -5102,7 +5101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="37" t="s">
         <v>72</v>
       </c>
